--- a/problems.xlsx
+++ b/problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\04526_03林　直基\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ED764C7-A885-480C-991F-217486B6753A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B00741-4F4D-40AC-8C6D-AF1E978AD374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4BA290A6-AF72-4671-8ACD-E2CE4EC1F809}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4BA290A6-AF72-4671-8ACD-E2CE4EC1F809}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -228,6 +228,56 @@
   </si>
   <si>
     <t>資料が添付されていません。送る前に確認するのが常識ではないでしょうか。再送してください。</t>
+  </si>
+  <si>
+    <t>3/16～3/19間で横持便を山陽⇒NXで15便、180PLの移動を予定しています。
+10トン車約11回分が浮く予定です。
+浮いた分が3/20・21の移動費に反映されますか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問21</t>
+    <rPh sb="0" eb="1">
+      <t>トイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金交渉。移転の運行車両について。移転日は4台にて4運行ずつ（計16運行を想定）</t>
+    <rPh sb="0" eb="2">
+      <t>リョウキン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウショウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イテン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ウンコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シャリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>イテンビ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ウンコウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ウンコウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ソウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -273,9 +323,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A15EB764-8349-46A1-89AC-B5032EAB251C}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.375" bestFit="1" customWidth="1"/>
@@ -850,6 +903,17 @@
         <v>62</v>
       </c>
     </row>
+    <row r="22" spans="1:3" ht="75" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/problems.xlsx
+++ b/problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\04526_03林　直基\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B00741-4F4D-40AC-8C6D-AF1E978AD374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4AA44D-69CC-4FEA-B2F1-3D7788787C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4BA290A6-AF72-4671-8ACD-E2CE4EC1F809}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>ID</t>
   </si>
@@ -53,48 +53,30 @@
     <t>問1</t>
   </si>
   <si>
-    <t>納期遅延の催促</t>
-  </si>
-  <si>
-    <t>昨日までが期限だったはずですが、まだ届いていません。忘れていたのでしょうか。こちらの予定が狂って非常に困っています。至急送ってください。</t>
-  </si>
-  <si>
     <t>問2</t>
   </si>
   <si>
     <t>指示と違う成果物</t>
   </si>
   <si>
-    <t>マニュアルを事前にお送りしたはずですが、なぜ違う方法で進められたのでしょうか。二度手間になるので、次からは勝手な判断をしないでください。</t>
-  </si>
-  <si>
     <t>問3</t>
   </si>
   <si>
     <t>急な依頼への断り</t>
   </si>
   <si>
-    <t>本日中に対応しろとのことですが、こちらも予定があります。物理的に不可能ですので、もっと余裕を持って依頼してください。</t>
-  </si>
-  <si>
     <t>問4</t>
   </si>
   <si>
     <t>他部署のミス指摘</t>
   </si>
   <si>
-    <t>御社の手配ミスで現場が混乱しています。もっと責任を持って確認してから連絡をいただけませんか。非常に迷惑しています。</t>
-  </si>
-  <si>
     <t>問5</t>
   </si>
   <si>
     <t>連絡漏れの指摘</t>
   </si>
   <si>
-    <t>重要な件はメールだけでなく、口頭でも伝えるべきではないでしょうか。聞いていなかったせいでトラブルになりました。以後気をつけてください。</t>
-  </si>
-  <si>
     <t>問6</t>
   </si>
   <si>
@@ -110,124 +92,61 @@
     <t>会議の欠席</t>
   </si>
   <si>
-    <t>その時間は別件で埋まっています。もっと早く調整してくれないと参加できません。次からは事前に予定を聞いてください。</t>
-  </si>
-  <si>
     <t>問8</t>
   </si>
   <si>
     <t>不十分な報告</t>
   </si>
   <si>
-    <t>報告書の内容が薄すぎて、何が言いたいのか分かりません。時間をかけて作成しているとは思えません。やり直してください。</t>
-  </si>
-  <si>
     <t>問9</t>
   </si>
   <si>
     <t>何度も同じ質問</t>
   </si>
   <si>
-    <t>それについては以前のメールで説明済みです。過去の履歴をしっかり確認してから質問していただけますか。</t>
-  </si>
-  <si>
     <t>問10</t>
   </si>
   <si>
-    <t>見積もりが高い</t>
-  </si>
-  <si>
-    <t>他社と比べて高すぎます。本当に精査されましたか？不信感しかありませんので、再検討してください。</t>
-  </si>
-  <si>
     <t>問11</t>
   </si>
   <si>
     <t>電話に出ない</t>
   </si>
   <si>
-    <t>何度もお電話していますが、つながりません。折り返しも遅すぎます。至急連絡をください。</t>
-  </si>
-  <si>
     <t>問12</t>
   </si>
   <si>
     <t>他人のミスのフォロー</t>
   </si>
   <si>
-    <t>本来私がやるべき仕事ではありませんが、放置できないので修正しました。自分の仕事には責任を持ってください。</t>
-  </si>
-  <si>
     <t>問13</t>
   </si>
   <si>
     <t>メールの返信が遅い</t>
   </si>
   <si>
-    <t>返信が遅すぎて、プロジェクトが止まっています。優先順位を考えて仕事をしていただかないと困ります。</t>
-  </si>
-  <si>
     <t>問14</t>
   </si>
   <si>
-    <t>ルールを守らない</t>
-  </si>
-  <si>
-    <t>共有事項は必ず守ってください。一人でも守らない人がいると、チーム全体の士気が下がります。自覚を持ってください。</t>
-  </si>
-  <si>
     <t>問15</t>
   </si>
   <si>
-    <t>責任の押し付け</t>
-  </si>
-  <si>
-    <t>それは私の担当外です。勝手に私の名前にしないでください。しかるべき部署に自分で確認してください。</t>
-  </si>
-  <si>
     <t>問16</t>
   </si>
   <si>
-    <t>誤字脱字の多さ</t>
-  </si>
-  <si>
-    <t>提出物に誤字が多すぎます。確認すれば防げるはずです。こちらに校正をさせないでください。</t>
-  </si>
-  <si>
     <t>問17</t>
   </si>
   <si>
-    <t>一方的な決定</t>
-  </si>
-  <si>
-    <t>相談もなく勝手に決められては困ります。私たちにも都合があります。事後報告ではなく事前に相談してください。</t>
-  </si>
-  <si>
     <t>問18</t>
   </si>
   <si>
     <t>態度の悪さへの不満</t>
   </si>
   <si>
-    <t>先日の会議での発言は、少し攻撃的すぎたのではありませんか。周囲も困惑していました。改めてください。</t>
-  </si>
-  <si>
     <t>問19</t>
   </si>
   <si>
-    <t>やる気への疑問</t>
-  </si>
-  <si>
-    <t>この程度のクオリティで満足されているのでしょうか。期待していただけに非常に残念です。再考を求めます。</t>
-  </si>
-  <si>
-    <t>問20</t>
-  </si>
-  <si>
     <t>資料の添付忘れ</t>
-  </si>
-  <si>
-    <t>資料が添付されていません。送る前に確認するのが常識ではないでしょうか。再送してください。</t>
   </si>
   <si>
     <t>3/16～3/19間で横持便を山陽⇒NXで15便、180PLの移動を予定しています。
@@ -236,14 +155,8 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>問21</t>
-    <rPh sb="0" eb="1">
-      <t>トイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>料金交渉。移転の運行車両について。移転日は4台にて4運行ずつ（計16運行を想定）</t>
+    <t>料金交渉。移転の運行車両について。移転日は4台にて4運行ずつ（計16運行×2日/512PLを想定）
+※倉庫には約700PLが保管されている</t>
     <rPh sb="0" eb="2">
       <t>リョウキン</t>
     </rPh>
@@ -274,8 +187,387 @@
     <rPh sb="34" eb="36">
       <t>ウンコウ</t>
     </rPh>
-    <rPh sb="37" eb="39">
+    <rPh sb="38" eb="39">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
       <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ソウコ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ホカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お世話になっております。
+昨日までが期限だったはずですが、まだ届いていません。
+忘れていたのでしょうか。こちらの予定が狂って非常に困っています。至急送ってください。</t>
+    <rPh sb="1" eb="3">
+      <t>セワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お世話になっております。
+本日中に対応しろとのことですが、こちらも予定があります。
+物理的に不可能ですので、もっと余裕を持って依頼してください。</t>
+    <rPh sb="1" eb="3">
+      <t>セワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お世話になっております。
+重要な件はメールだけでなく、口頭でも伝えるべきではないでしょうか。
+聞いていなかったせいでトラブルになりました。以後気をつけてください。</t>
+    <rPh sb="1" eb="3">
+      <t>セワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お世話になっております。
+それについては以前のメールで説明済みです。
+過去の履歴をしっかり確認してから質問していただけますか。</t>
+    <rPh sb="1" eb="3">
+      <t>セワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">お疲れ様です。
+コピペされただけの資料を見て、こちらはどうすればいいのでしょうか。
+この内容では決裁できません。
+</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ケッサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お世話になっております。
+報告書の内容が薄すぎて、何が言いたいのか分かりません。
+ちゃんと検証されているのでしょうか。
+この内容では受領できません。</t>
+    <rPh sb="1" eb="3">
+      <t>セワ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ジュリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お世話になっております。
+何度もお電話していますが、つながりません。
+折り返しもいただけないことに驚いています。
+至急連絡をいただけますか。</t>
+    <rPh sb="1" eb="3">
+      <t>セワ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>オドロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お疲れ様です。
+忙しいことは分かりますが、あなたのせいでプロジェクトに遅延が発生しています。
+全員に迷惑が掛かっているので優先順位を考えて仕事をしてください。</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イソガ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>チエン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>メイワク</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お疲れ様です。
+誰の判断で進めたのでしょうか。
+社内のルールを知らないのであれば聞くべきだと思いますが、どうお考えでしょうか。
+事後報告で仕事をするように教わってきたのでしょうか。</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シャナイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="64" eb="68">
+      <t>ジゴホウコク</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お疲れ様です。
+先日の会議での発言について攻撃的すぎだったと感じています。
+周囲も困惑していました。
+周囲の受け止め方も考えて発言しましょう。</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ハツゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お疲れ様です。
+資料が添付されていませんが？
+再送してください。</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お疲れ様です。
+貴部の手配ミスで現場が混乱いたしました。
+もっと責任を持って確認してから連絡をいただけませんか。
+現場の負担が増加して非常に迷惑しています。</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キブ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ゲンバ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>フタン</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お疲れ様です。
+その時間は別件で埋まっています。
+もっと早く調整してくれないと参加できません。
+次からは事前に予定を聞いてください。</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お疲れ様です。
+問い合わせへの対応はこちらでやっておきました。
+本来であればそちらで対応すべき内容です。
+自分の仕事には責任を持って取り組んでください。</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お疲れ様です。
+ルールは必ず守ってください。あなたが守らないことで秩序が乱れますし、
+チーム全体の士気が下がります。
+自覚を持っ行動するようにしてください。</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>マモ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>チツジョ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ミダ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>納期遅延の催促</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お疲れ様です。
+マニュアルを事前にお送りしたはずですが、違う方法で進められた理由を教えてください。
+二度手間になるので、次からは勝手な判断をしないでください。</t>
+    <rPh sb="1" eb="2">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルール遵守の指導</t>
+    <rPh sb="3" eb="5">
+      <t>ジュンシュ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一方的な決定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コピペ資料（内容不備）への叱責</t>
+    <rPh sb="3" eb="5">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>フビ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シッセキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -665,14 +957,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A15EB764-8349-46A1-89AC-B5032EAB251C}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="53.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.375" customWidth="1"/>
     <col min="3" max="3" width="141.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -683,237 +975,210 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="C6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    <row r="8" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="75" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C9" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+      <c r="B20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="75" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
+    </row>
+    <row r="22" spans="1:3" ht="77.25" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/problems.xlsx
+++ b/problems.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\04526_03林　直基\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sanyoju-my.sharepoint.com/personal/hayashi_n_sanyoju_onmicrosoft_com/Documents/林2/010_業務・品質/999_アプリけーション/メール採点アプリ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4AA44D-69CC-4FEA-B2F1-3D7788787C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{DD4AA44D-69CC-4FEA-B2F1-3D7788787C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27941391-2CC8-4C96-B9FB-5219C66E1A40}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4BA290A6-AF72-4671-8ACD-E2CE4EC1F809}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -568,6 +568,69 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>シッセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">毎度大変お世話になっております。
+下記件ですが、本日立ち合いの際、磯崎共に確認いただいたと思いますが、
+消火器上以外であれば、導線含めて許可できませんので、
+当社のライン配置、人員とモノの導線とは関係ないと思います。
+原則、Aエリアへの設置は、すべてNX側にも申請しているため、追加は行いたくありません。
+また、Aエリアに設置して、Cエリアまでの電波等届くのでしょうか？
+Bエリア、Cエリアのネットワークをご利用頂くか、事務所（食堂内）への設置はいかがでしょうか？
+作業場内に勤怠用のネットワークを置くこと自体、問題と考えます。
+宜しくお願い致します。
+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネットワーク機器の置き場所の相談
+背景：事前現調に不手際があり、再々調整にて担当者と合意が得られたものの、先方の上席から設置位置について否決されている。</t>
+    <rPh sb="6" eb="8">
+      <t>キキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソウダン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>ジゼンゲンチョウ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>フテギワ</t>
+    </rPh>
+    <rPh sb="32" eb="36">
+      <t>サイサイチョウセイ</t>
+    </rPh>
+    <rPh sb="38" eb="41">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ゴウイ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>センポウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ジョウセキ</t>
+    </rPh>
+    <rPh sb="60" eb="64">
+      <t>セッチイチ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ヒケツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1162,9 +1225,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="187.5" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>32</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.4">
